--- a/business_registration_forms/017_corporate_partner_information_form--business_registration_forms.xlsx
+++ b/business_registration_forms/017_corporate_partner_information_form--business_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'limited'}</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Limited'}</t>
+          <t>Limited</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unlimited'}</t>
+          <t>unlimited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Unlimited'}</t>
+          <t>Unlimited</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'healthcare'}</t>
+          <t>healthcare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Healthcare'}</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'ceo'}</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'CEO'}</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'coo'}</t>
+          <t>coo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'COO'}</t>
+          <t>COO</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'terms_and_conditions'}</t>
+          <t>terms_and_conditions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Terms and Conditions'}</t>
+          <t>Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'acceptance_of_terms'}</t>
+          <t>acceptance_of_terms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Acceptance of Terms'}</t>
+          <t>Acceptance of Terms</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'privacy_and_data_security'}</t>
+          <t>privacy_and_data_security</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Privacy and Data Security'}</t>
+          <t>Privacy and Data Security</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'acceptance_of_privacy'}</t>
+          <t>acceptance_of_privacy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Acceptance of Privacy'}</t>
+          <t>Acceptance of Privacy</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
